--- a/AAII_Financials/Yearly/SKYE_YR_FIN.xlsx
+++ b/AAII_Financials/Yearly/SKYE_YR_FIN.xlsx
@@ -954,10 +954,10 @@
         <v>-400</v>
       </c>
       <c r="E14" s="3">
-        <v>-1400</v>
+        <v>-7600</v>
       </c>
       <c r="F14" s="3">
-        <v>23300</v>
+        <v>23200</v>
       </c>
       <c r="G14" s="3">
         <v>500</v>
@@ -1053,10 +1053,10 @@
         <v>58200</v>
       </c>
       <c r="E17" s="3">
-        <v>30200</v>
+        <v>36400</v>
       </c>
       <c r="F17" s="3">
-        <v>13500</v>
+        <v>13700</v>
       </c>
       <c r="G17" s="3">
         <v>18300</v>
@@ -1095,10 +1095,10 @@
         <v>-58200</v>
       </c>
       <c r="E18" s="3">
-        <v>-30200</v>
+        <v>-36400</v>
       </c>
       <c r="F18" s="3">
-        <v>-13500</v>
+        <v>-13700</v>
       </c>
       <c r="G18" s="3">
         <v>-18300</v>
@@ -1197,10 +1197,10 @@
         <v>-57400</v>
       </c>
       <c r="E21" s="3">
-        <v>-29900</v>
+        <v>-36100</v>
       </c>
       <c r="F21" s="3">
-        <v>-13400</v>
+        <v>-13500</v>
       </c>
       <c r="G21" s="3">
         <v>-18300</v>
